--- a/themes/commission.xlsx
+++ b/themes/commission.xlsx
@@ -499,12 +499,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">          · По счету — с комиссией, размер комиссии можно уточнить на [сайте](https://uralsib.ru/tarify) в разделе «Денежные переводы».</t>
+          <t xml:space="preserve">          · По счету — с комиссией, размер комиссии можно уточнить на [сайте](https://uralsib.ru/tarify) в разделе «Денежные переводы»</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>эн-дефис заменён на тире; добавлена точка в конце предложения</t>
+          <t>эн-дефис заменён на тире</t>
         </is>
       </c>
     </row>
